--- a/Codelist Excel Files and Conversion Templates to XML/gridPattern.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/gridPattern.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes naming the plan arrangement of rigid inclusion columns within a design. These codes are used for the value of the gridPattern property of the diggs:RIColumnDesign object. Where the design's scope carries a plannedPositions grid, the grid's offsetVectors define the lattice exactly and this code merely names what they already express; where scope carries no grid, this property and the column spacings are the prevailing statement of the layout. The list is open.</t>
+          <t>Codes naming the plan arrangement of rigid inclusion columns within a design. These codes are used for the value of the gridPattern property of the diggs:DesignRIColumn object. Where the design's scope carries a plannedPositions grid, the grid's offsetVectors define the lattice exactly and this code merely names what they already express; where scope carries no grid, this property and the column spacings are the prevailing statement of the layout. The list is open.</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>//diggs:RIColumnDesign/diggs:gridPattern</t>
+          <t>//diggs:DesignRIColumn/diggs:gridPattern</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>//diggs:RIColumnDesign/diggs:gridPattern</t>
+          <t>//diggs:DesignRIColumn/diggs:gridPattern</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>//diggs:RIColumnDesign/diggs:gridPattern</t>
+          <t>//diggs:DesignRIColumn/diggs:gridPattern</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>//diggs:RIColumnDesign/diggs:gridPattern</t>
+          <t>//diggs:DesignRIColumn/diggs:gridPattern</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>//diggs:RIColumnDesign/diggs:gridPattern</t>
+          <t>//diggs:DesignRIColumn/diggs:gridPattern</t>
         </is>
       </c>
     </row>
